--- a/Result/profitability/4526.xlsx
+++ b/Result/profitability/4526.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1</v>
+        <v>-0.07875000000000006</v>
       </c>
       <c r="N2" t="n">
-        <v>13.93875</v>
+        <v>14.765</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0.11</v>
+        <v>0.3174999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>15.635</v>
+        <v>18.1975</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5137499999999999</v>
+        <v>0.45</v>
       </c>
       <c r="N4" t="n">
-        <v>19.41625</v>
+        <v>19.14</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.48</v>
+        <v>0.1299999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>19.88125</v>
+        <v>20.235</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2275</v>
+        <v>0.175</v>
       </c>
       <c r="N6" t="n">
-        <v>22.15</v>
+        <v>21.7975</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.205</v>
+        <v>0.26</v>
       </c>
       <c r="N7" t="n">
-        <v>22.62</v>
+        <v>23.89</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>0.295</v>
+        <v>0.33</v>
       </c>
       <c r="N8" t="n">
-        <v>24.65875</v>
+        <v>25.37375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.24</v>
       </c>
       <c r="M13" t="n">
-        <v>0.44</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>25.62</v>
@@ -9344,27 +9344,27 @@
         <v>14.99</v>
       </c>
       <c r="G71" t="n">
-        <v>-239</v>
+        <v>-240</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-18.52%</t>
+          <t>-18.62%</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>959</v>
       </c>
       <c r="J71" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="K71" t="n">
         <v>617</v>
       </c>
       <c r="L71" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.09000000000000002</v>
+        <v>-0.09125000000000005</v>
       </c>
       <c r="N71" t="n">
         <v>13.86375</v>
@@ -9394,10 +9394,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="X71" t="n">
-        <v>17.69230769230769</v>
+        <v>17.61538461538461</v>
       </c>
       <c r="Y71" t="n">
         <v>-5.040000000000001</v>
@@ -9406,10 +9406,10 @@
         <v>-0.2516225661507738</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="AB71" t="n">
-        <v>-5.339285714285714</v>
+        <v>-5.321428571428571</v>
       </c>
       <c r="AC71" t="n">
         <v>0.5899999999999999</v>
@@ -9471,27 +9471,27 @@
         <v>20.64</v>
       </c>
       <c r="G72" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-9.62%</t>
+          <t>-9.51%</t>
         </is>
       </c>
       <c r="I72" t="n">
         <v>131</v>
       </c>
       <c r="J72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L72" t="n">
         <v>0.05</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.08875000000000002</v>
+        <v>-0.09000000000000005</v>
       </c>
       <c r="N72" t="n">
         <v>13.76875</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>-2.38</v>
+        <v>-2.37</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.9794238683127572</v>
+        <v>-0.9793388429752066</v>
       </c>
       <c r="Y72" t="n">
         <v>5.65</v>
@@ -9618,7 +9618,7 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.22</v>
+        <v>-0.2212500000000001</v>
       </c>
       <c r="N73" t="n">
         <v>12.68</v>
@@ -9745,7 +9745,7 @@
         <v>-0.65</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.2500000000000001</v>
+        <v>-0.2512500000000001</v>
       </c>
       <c r="N74" t="n">
         <v>12.29375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1551</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1274</v>
+      </c>
+      <c r="E75" t="n">
+        <v>276</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-84</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-68</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-94</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2275000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.72125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4307692307692308</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.720000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4727272727272729</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.152892561983471</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1887925283522349</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
